--- a/_build/interestelar_100.xlsx
+++ b/_build/interestelar_100.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebasaluuclm-my.sharepoint.com/personal/miguelangel_tarancon_uclm_es/Documents/Documentos/curso/Cursos de Datos/New Book/RStars-book/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebasaluuclm-my.sharepoint.com/personal/miguelangel_tarancon_uclm_es/Documents/Documentos/curso/material MAAEE/Curso 24_25/R Lite/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="69" documentId="8_{B3B75BCC-7F0B-4E4C-AD29-B2AC76E43FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA021B26-35C8-4817-9427-3589582F3C0D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inicio" sheetId="1" r:id="rId1"/>
@@ -1000,6 +1000,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{24844CFD-BDB6-42DA-A301-5814728C3E15}" name="Tabla2" displayName="Tabla2" ref="A1:C27" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
   <autoFilter ref="A1:C27" xr:uid="{24844CFD-BDB6-42DA-A301-5814728C3E15}">

--- a/_build/interestelar_100.xlsx
+++ b/_build/interestelar_100.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="217">
   <si>
-    <t>con intereses puramente didácticos.</t>
+    <t>sin relación con sus titulares ni respaldo por su parte. Aviso completo en el capítulo «Licencia» de los libros del universo R-Stars.</t>
   </si>
   <si>
     <t>Variable</t>
@@ -692,7 +692,7 @@
     <t>Valor total de los recursos de la empresa.</t>
   </si>
   <si>
-    <t>Los nombres de las empresas y sus sedes se han inspirado en distintas fuentes de la filmografía de ciencia ficción,</t>
+    <t>Algunos nombres de compañías, sedes y personajes se inspiran en sagas de ciencia ficción y se usan solo como homenaje, con fines creativos y didácticos,</t>
   </si>
 </sst>
 </file>
